--- a/quiz_template/data/quizzes_image.xlsx
+++ b/quiz_template/data/quizzes_image.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E70"/>
+  <dimension ref="A1:E80"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -468,14 +468,14 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Ape</t>
+          <t>Bison</t>
         </is>
       </c>
       <c r="D2" t="n">
         <v>5</v>
       </c>
       <c r="E2" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="3">
@@ -491,14 +491,14 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Deer</t>
+          <t>Chimpanzee</t>
         </is>
       </c>
       <c r="D3" t="n">
         <v>5</v>
       </c>
       <c r="E3" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="4">
@@ -514,14 +514,14 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Raccoon</t>
+          <t>Giraffe</t>
         </is>
       </c>
       <c r="D4" t="n">
         <v>5</v>
       </c>
       <c r="E4" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="5">
@@ -537,14 +537,14 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Rhinoceros</t>
+          <t>Hippopotamus</t>
         </is>
       </c>
       <c r="D5" t="n">
         <v>5</v>
       </c>
       <c r="E5" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="6">
@@ -560,260 +560,260 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Zebra</t>
+          <t>Jaguar</t>
         </is>
       </c>
       <c r="D6" t="n">
         <v>5</v>
       </c>
       <c r="E6" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Flag</t>
+          <t>Animal</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Guess the name of this Flag?</t>
+          <t>Guess the name of this Animal?</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Afghanistan</t>
+          <t>Kangaroo</t>
         </is>
       </c>
       <c r="D7" t="n">
         <v>5</v>
       </c>
       <c r="E7" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Flag</t>
+          <t>Animal</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Guess the name of this Flag?</t>
+          <t>Guess the name of this Animal?</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Austria</t>
+          <t>Koala</t>
         </is>
       </c>
       <c r="D8" t="n">
         <v>5</v>
       </c>
       <c r="E8" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Flag</t>
+          <t>Animal</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Guess the name of this Flag?</t>
+          <t>Guess the name of this Animal?</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Azerbaijan</t>
+          <t>Panda</t>
         </is>
       </c>
       <c r="D9" t="n">
         <v>5</v>
       </c>
       <c r="E9" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Flag</t>
+          <t>Animal</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Guess the name of this Flag?</t>
+          <t>Guess the name of this Animal?</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Bahrain</t>
+          <t>Wolf</t>
         </is>
       </c>
       <c r="D10" t="n">
         <v>5</v>
       </c>
       <c r="E10" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Flag</t>
+          <t>Animal</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Guess the name of this Flag?</t>
+          <t>Guess the name of this Animal?</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Bhutan</t>
+          <t>Zebra</t>
         </is>
       </c>
       <c r="D11" t="n">
         <v>5</v>
       </c>
       <c r="E11" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Flag</t>
+          <t>Dog Breed</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Guess the name of this Flag?</t>
+          <t>Guess the name of this Dog Breed?</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Bolivia</t>
+          <t>Beagle</t>
         </is>
       </c>
       <c r="D12" t="n">
         <v>5</v>
       </c>
       <c r="E12" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Flag</t>
+          <t>Dog Breed</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Guess the name of this Flag?</t>
+          <t>Guess the name of this Dog Breed?</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Brazil</t>
+          <t>German Shepherd</t>
         </is>
       </c>
       <c r="D13" t="n">
         <v>5</v>
       </c>
       <c r="E13" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Flag</t>
+          <t>Dog Breed</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Guess the name of this Flag?</t>
+          <t>Guess the name of this Dog Breed?</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Burkina Faso</t>
+          <t>Golden Retriever</t>
         </is>
       </c>
       <c r="D14" t="n">
         <v>5</v>
       </c>
       <c r="E14" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Flag</t>
+          <t>Dog Breed</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Guess the name of this Flag?</t>
+          <t>Guess the name of this Dog Breed?</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Cambodia</t>
+          <t>Labrador</t>
         </is>
       </c>
       <c r="D15" t="n">
         <v>5</v>
       </c>
       <c r="E15" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Flag</t>
+          <t>Dog Breed</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Guess the name of this Flag?</t>
+          <t>Guess the name of this Dog Breed?</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Cameroon</t>
+          <t>Pitbull</t>
         </is>
       </c>
       <c r="D16" t="n">
         <v>5</v>
       </c>
       <c r="E16" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Flag</t>
+          <t>Famous musician</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Guess the name of this Flag?</t>
+          <t>Guess the name of this Famous musician?</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Canada</t>
+          <t>Aretha Franklin</t>
         </is>
       </c>
       <c r="D17" t="n">
@@ -826,17 +826,17 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Flag</t>
+          <t>Famous musician</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Guess the name of this Flag?</t>
+          <t>Guess the name of this Famous musician?</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>China</t>
+          <t>Ariana Grande</t>
         </is>
       </c>
       <c r="D18" t="n">
@@ -849,17 +849,17 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Flag</t>
+          <t>Famous musician</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Guess the name of this Flag?</t>
+          <t>Guess the name of this Famous musician?</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Costa Rica</t>
+          <t>Beyonce</t>
         </is>
       </c>
       <c r="D19" t="n">
@@ -872,17 +872,17 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Flag</t>
+          <t>Famous musician</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Guess the name of this Flag?</t>
+          <t>Guess the name of this Famous musician?</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Croatia</t>
+          <t>Billie Eilish</t>
         </is>
       </c>
       <c r="D20" t="n">
@@ -895,17 +895,17 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Flag</t>
+          <t>Famous musician</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Guess the name of this Flag?</t>
+          <t>Guess the name of this Famous musician?</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Czech republic</t>
+          <t>Bob Dylan</t>
         </is>
       </c>
       <c r="D21" t="n">
@@ -918,17 +918,17 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Flag</t>
+          <t>Famous musician</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Guess the name of this Flag?</t>
+          <t>Guess the name of this Famous musician?</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Dominica</t>
+          <t>Bruno Mars</t>
         </is>
       </c>
       <c r="D22" t="n">
@@ -941,17 +941,17 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Flag</t>
+          <t>Famous musician</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Guess the name of this Flag?</t>
+          <t>Guess the name of this Famous musician?</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Dominican republic</t>
+          <t>David Bowie</t>
         </is>
       </c>
       <c r="D23" t="n">
@@ -964,17 +964,17 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Flag</t>
+          <t>Famous musician</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Guess the name of this Flag?</t>
+          <t>Guess the name of this Famous musician?</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Ecuador</t>
+          <t>Ed Sheeran</t>
         </is>
       </c>
       <c r="D24" t="n">
@@ -987,17 +987,17 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Flag</t>
+          <t>Famous musician</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Guess the name of this Flag?</t>
+          <t>Guess the name of this Famous musician?</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Egypt</t>
+          <t>Elvis Presley</t>
         </is>
       </c>
       <c r="D25" t="n">
@@ -1010,17 +1010,17 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Flag</t>
+          <t>Famous musician</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Guess the name of this Flag?</t>
+          <t>Guess the name of this Famous musician?</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>El salvador</t>
+          <t>Frank Sinatra</t>
         </is>
       </c>
       <c r="D26" t="n">
@@ -1033,17 +1033,17 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Flag</t>
+          <t>Famous musician</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Guess the name of this Flag?</t>
+          <t>Guess the name of this Famous musician?</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Eritrea</t>
+          <t>Freddie Mercury</t>
         </is>
       </c>
       <c r="D27" t="n">
@@ -1056,17 +1056,17 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Flag</t>
+          <t>Famous musician</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Guess the name of this Flag?</t>
+          <t>Guess the name of this Famous musician?</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Finland</t>
+          <t>Jimi Hendrix</t>
         </is>
       </c>
       <c r="D28" t="n">
@@ -1079,17 +1079,17 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Flag</t>
+          <t>Famous musician</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Guess the name of this Flag?</t>
+          <t>Guess the name of this Famous musician?</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Germany</t>
+          <t>Justin Bieber</t>
         </is>
       </c>
       <c r="D29" t="n">
@@ -1102,17 +1102,17 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Flag</t>
+          <t>Famous musician</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Guess the name of this Flag?</t>
+          <t>Guess the name of this Famous musician?</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Hungary</t>
+          <t>Kurt Cobain</t>
         </is>
       </c>
       <c r="D30" t="n">
@@ -1125,17 +1125,17 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Flag</t>
+          <t>Famous musician</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Guess the name of this Flag?</t>
+          <t>Guess the name of this Famous musician?</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Kurdistan</t>
+          <t>Lady Gaga</t>
         </is>
       </c>
       <c r="D31" t="n">
@@ -1148,17 +1148,17 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Flag</t>
+          <t>Famous musician</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Guess the name of this Flag?</t>
+          <t>Guess the name of this Famous musician?</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>France</t>
+          <t>Led Zeppelin</t>
         </is>
       </c>
       <c r="D32" t="n">
@@ -1171,17 +1171,17 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Flag</t>
+          <t>Famous musician</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Guess the name of this Flag?</t>
+          <t>Guess the name of this Famous musician?</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Jordan</t>
+          <t>Madonna</t>
         </is>
       </c>
       <c r="D33" t="n">
@@ -1194,17 +1194,17 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Flag</t>
+          <t>Famous musician</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Guess the name of this Flag?</t>
+          <t>Guess the name of this Famous musician?</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Pakistan</t>
+          <t>Pink Floyd</t>
         </is>
       </c>
       <c r="D34" t="n">
@@ -1227,7 +1227,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Aretha Franklin</t>
+          <t>Prince</t>
         </is>
       </c>
       <c r="D35" t="n">
@@ -1250,7 +1250,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Ariana Grande</t>
+          <t>Rihanna</t>
         </is>
       </c>
       <c r="D36" t="n">
@@ -1273,7 +1273,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Beyonce</t>
+          <t>Stevie Wonder</t>
         </is>
       </c>
       <c r="D37" t="n">
@@ -1296,7 +1296,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Billie Eilish</t>
+          <t>Taylor Swift</t>
         </is>
       </c>
       <c r="D38" t="n">
@@ -1319,7 +1319,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Bob Dylan</t>
+          <t>The Beatles</t>
         </is>
       </c>
       <c r="D39" t="n">
@@ -1342,7 +1342,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Bruno Mars</t>
+          <t>The Rolling Stones</t>
         </is>
       </c>
       <c r="D40" t="n">
@@ -1365,7 +1365,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>David Bowie</t>
+          <t>The Weeknd</t>
         </is>
       </c>
       <c r="D41" t="n">
@@ -1388,7 +1388,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Ed Sheeran</t>
+          <t>Whitney Houston</t>
         </is>
       </c>
       <c r="D42" t="n">
@@ -1401,17 +1401,17 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Famous musician</t>
+          <t>Famous person</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Guess the name of this Famous musician?</t>
+          <t>Guess the name of this Famous person?</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Elvis Presley</t>
+          <t>Nikola Tesla</t>
         </is>
       </c>
       <c r="D43" t="n">
@@ -1424,17 +1424,17 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Famous musician</t>
+          <t>Famous person</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Guess the name of this Famous musician?</t>
+          <t>Guess the name of this Famous person?</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Frank Sinatra</t>
+          <t>Albert Einstein</t>
         </is>
       </c>
       <c r="D44" t="n">
@@ -1447,17 +1447,17 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Famous musician</t>
+          <t>Famous person</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Guess the name of this Famous musician?</t>
+          <t>Guess the name of this Famous person?</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Freddie Mercury</t>
+          <t>Leonardo da Vinci</t>
         </is>
       </c>
       <c r="D45" t="n">
@@ -1470,17 +1470,17 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Famous musician</t>
+          <t>Famous person</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Guess the name of this Famous musician?</t>
+          <t>Guess the name of this Famous person?</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Jimi Hendrix</t>
+          <t>Mahatma Gandhi</t>
         </is>
       </c>
       <c r="D46" t="n">
@@ -1493,17 +1493,17 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Famous musician</t>
+          <t>Famous person</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Guess the name of this Famous musician?</t>
+          <t>Guess the name of this Famous person?</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Justin Bieber</t>
+          <t>Michael Jackson</t>
         </is>
       </c>
       <c r="D47" t="n">
@@ -1516,17 +1516,17 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Famous musician</t>
+          <t>Famous person</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Guess the name of this Famous musician?</t>
+          <t>Guess the name of this Famous person?</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Kurt Cobain</t>
+          <t>Nelson Mandela</t>
         </is>
       </c>
       <c r="D48" t="n">
@@ -1539,17 +1539,17 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Famous musician</t>
+          <t>Famous person</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Guess the name of this Famous musician?</t>
+          <t>Guess the name of this Famous person?</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Lady Gaga</t>
+          <t>Oprah Winfrey</t>
         </is>
       </c>
       <c r="D49" t="n">
@@ -1562,17 +1562,17 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Famous musician</t>
+          <t>Famous person</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Guess the name of this Famous musician?</t>
+          <t>Guess the name of this Famous person?</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Led Zeppelin</t>
+          <t>Princess Diana</t>
         </is>
       </c>
       <c r="D50" t="n">
@@ -1585,17 +1585,17 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Famous musician</t>
+          <t>Famous person</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Guess the name of this Famous musician?</t>
+          <t>Guess the name of this Famous person?</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Madonna</t>
+          <t>Sir Isaac Newton</t>
         </is>
       </c>
       <c r="D51" t="n">
@@ -1608,17 +1608,17 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Famous musician</t>
+          <t>Famous person</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Guess the name of this Famous musician?</t>
+          <t>Guess the name of this Famous person?</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Pink Floyd</t>
+          <t>William Shakespeare</t>
         </is>
       </c>
       <c r="D52" t="n">
@@ -1631,17 +1631,17 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Famous musician</t>
+          <t>Flag</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Guess the name of this Famous musician?</t>
+          <t>Guess the name of this Flag?</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Prince</t>
+          <t>Afghanistan</t>
         </is>
       </c>
       <c r="D53" t="n">
@@ -1654,17 +1654,17 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Famous musician</t>
+          <t>Flag</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Guess the name of this Famous musician?</t>
+          <t>Guess the name of this Flag?</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Rihanna</t>
+          <t>Austria</t>
         </is>
       </c>
       <c r="D54" t="n">
@@ -1677,17 +1677,17 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Famous musician</t>
+          <t>Flag</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Guess the name of this Famous musician?</t>
+          <t>Guess the name of this Flag?</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Stevie Wonder</t>
+          <t>Azerbaijan</t>
         </is>
       </c>
       <c r="D55" t="n">
@@ -1700,17 +1700,17 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Famous musician</t>
+          <t>Flag</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Guess the name of this Famous musician?</t>
+          <t>Guess the name of this Flag?</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Taylor Swift</t>
+          <t>Bahrain</t>
         </is>
       </c>
       <c r="D56" t="n">
@@ -1723,17 +1723,17 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Famous musician</t>
+          <t>Flag</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Guess the name of this Famous musician?</t>
+          <t>Guess the name of this Flag?</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>The Beatles</t>
+          <t>Bhutan</t>
         </is>
       </c>
       <c r="D57" t="n">
@@ -1746,17 +1746,17 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Famous musician</t>
+          <t>Flag</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Guess the name of this Famous musician?</t>
+          <t>Guess the name of this Flag?</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>The Rolling Stones</t>
+          <t>Bolivia</t>
         </is>
       </c>
       <c r="D58" t="n">
@@ -1769,17 +1769,17 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Famous musician</t>
+          <t>Flag</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Guess the name of this Famous musician?</t>
+          <t>Guess the name of this Flag?</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>The Weeknd</t>
+          <t>Brazil</t>
         </is>
       </c>
       <c r="D59" t="n">
@@ -1792,17 +1792,17 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Famous musician</t>
+          <t>Flag</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Guess the name of this Famous musician?</t>
+          <t>Guess the name of this Flag?</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Whitney Houston</t>
+          <t>Burkina Faso</t>
         </is>
       </c>
       <c r="D60" t="n">
@@ -1815,17 +1815,17 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Famous person</t>
+          <t>Flag</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Guess the name of this Famous person?</t>
+          <t>Guess the name of this Flag?</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Nikola Tesla</t>
+          <t>Cambodia</t>
         </is>
       </c>
       <c r="D61" t="n">
@@ -1838,17 +1838,17 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Famous person</t>
+          <t>Flag</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Guess the name of this Famous person?</t>
+          <t>Guess the name of this Flag?</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Albert Einstein</t>
+          <t>Cameroon</t>
         </is>
       </c>
       <c r="D62" t="n">
@@ -1861,17 +1861,17 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Famous person</t>
+          <t>Flag</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Guess the name of this Famous person?</t>
+          <t>Guess the name of this Flag?</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Leonardo da Vinci</t>
+          <t>Canada</t>
         </is>
       </c>
       <c r="D63" t="n">
@@ -1884,17 +1884,17 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Famous person</t>
+          <t>Flag</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Guess the name of this Famous person?</t>
+          <t>Guess the name of this Flag?</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Mahatma Gandhi</t>
+          <t>China</t>
         </is>
       </c>
       <c r="D64" t="n">
@@ -1907,17 +1907,17 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Famous person</t>
+          <t>Flag</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Guess the name of this Famous person?</t>
+          <t>Guess the name of this Flag?</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Michael Jackson</t>
+          <t>Costa Rica</t>
         </is>
       </c>
       <c r="D65" t="n">
@@ -1930,17 +1930,17 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Famous person</t>
+          <t>Flag</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Guess the name of this Famous person?</t>
+          <t>Guess the name of this Flag?</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Nelson Mandela</t>
+          <t>Croatia</t>
         </is>
       </c>
       <c r="D66" t="n">
@@ -1953,17 +1953,17 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Famous person</t>
+          <t>Flag</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Guess the name of this Famous person?</t>
+          <t>Guess the name of this Flag?</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Oprah Winfrey</t>
+          <t>Czech republic</t>
         </is>
       </c>
       <c r="D67" t="n">
@@ -1976,17 +1976,17 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Famous person</t>
+          <t>Flag</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Guess the name of this Famous person?</t>
+          <t>Guess the name of this Flag?</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Princess Diana</t>
+          <t>Dominica</t>
         </is>
       </c>
       <c r="D68" t="n">
@@ -1999,17 +1999,17 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Famous person</t>
+          <t>Flag</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Guess the name of this Famous person?</t>
+          <t>Guess the name of this Flag?</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Sir Isaac Newton</t>
+          <t>Dominican republic</t>
         </is>
       </c>
       <c r="D69" t="n">
@@ -2022,23 +2022,253 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Famous person</t>
+          <t>Flag</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Guess the name of this Famous person?</t>
+          <t>Guess the name of this Flag?</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>William Shakespeare</t>
+          <t>Ecuador</t>
         </is>
       </c>
       <c r="D70" t="n">
         <v>5</v>
       </c>
       <c r="E70" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>Flag</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>Guess the name of this Flag?</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>Egypt</t>
+        </is>
+      </c>
+      <c r="D71" t="n">
+        <v>5</v>
+      </c>
+      <c r="E71" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>Flag</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>Guess the name of this Flag?</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>El salvador</t>
+        </is>
+      </c>
+      <c r="D72" t="n">
+        <v>5</v>
+      </c>
+      <c r="E72" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>Flag</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>Guess the name of this Flag?</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>Eritrea</t>
+        </is>
+      </c>
+      <c r="D73" t="n">
+        <v>5</v>
+      </c>
+      <c r="E73" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>Flag</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>Guess the name of this Flag?</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>Finland</t>
+        </is>
+      </c>
+      <c r="D74" t="n">
+        <v>5</v>
+      </c>
+      <c r="E74" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>Flag</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>Guess the name of this Flag?</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="D75" t="n">
+        <v>5</v>
+      </c>
+      <c r="E75" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>Flag</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>Guess the name of this Flag?</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>Hungary</t>
+        </is>
+      </c>
+      <c r="D76" t="n">
+        <v>5</v>
+      </c>
+      <c r="E76" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>Flag</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>Guess the name of this Flag?</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>Kurdistan</t>
+        </is>
+      </c>
+      <c r="D77" t="n">
+        <v>5</v>
+      </c>
+      <c r="E77" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>Flag</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>Guess the name of this Flag?</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>France</t>
+        </is>
+      </c>
+      <c r="D78" t="n">
+        <v>5</v>
+      </c>
+      <c r="E78" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>Flag</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>Guess the name of this Flag?</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>Jordan</t>
+        </is>
+      </c>
+      <c r="D79" t="n">
+        <v>5</v>
+      </c>
+      <c r="E79" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>Flag</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>Guess the name of this Flag?</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>Pakistan</t>
+        </is>
+      </c>
+      <c r="D80" t="n">
+        <v>5</v>
+      </c>
+      <c r="E80" t="b">
         <v>0</v>
       </c>
     </row>
